--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF40D010-EB8E-4EA9-9A23-512518377C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A1866C-7492-407A-9243-C861163ED14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -90,127 +90,46 @@
     <t xml:space="preserve">Total </t>
   </si>
   <si>
-    <t xml:space="preserve">HA Mega Mart </t>
-  </si>
-  <si>
     <t>Delivered</t>
   </si>
   <si>
-    <t xml:space="preserve">LUTF Mart </t>
-  </si>
-  <si>
-    <t>Aslam Mart LDA</t>
-  </si>
-  <si>
-    <t>Ss Departmental Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raheem </t>
-  </si>
-  <si>
-    <t>Risen Gajumata</t>
-  </si>
-  <si>
-    <t>Zohra Mart</t>
-  </si>
-  <si>
-    <t>Sohail Traders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinix </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gourmet Foods </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gourmet Behria Town </t>
-  </si>
-  <si>
-    <t>Imperia Departmental Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rainbow Shadra </t>
-  </si>
-  <si>
-    <t>Rainbow Shikhupura</t>
-  </si>
-  <si>
-    <t>Rainbow Gujranwala</t>
-  </si>
-  <si>
-    <t>Zubaida Associates</t>
-  </si>
-  <si>
-    <t>Green Velly</t>
-  </si>
-  <si>
-    <t>Rainbow Defence Road</t>
-  </si>
-  <si>
-    <t>Rainbow EME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rainbow Wapda Town </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rainbow Model Town </t>
-  </si>
-  <si>
     <t>Primary</t>
   </si>
   <si>
-    <t xml:space="preserve">Rainbow Behria Town </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/7 Mart </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euro Rachna Block </t>
-  </si>
-  <si>
-    <t>HKB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risen Gajumata </t>
-  </si>
-  <si>
-    <t>Nabeel Traders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goutmet MIX </t>
-  </si>
-  <si>
-    <t>Rainbow Barki Road</t>
-  </si>
-  <si>
-    <t>Euro Fateh Ghar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jalal Sons </t>
   </si>
   <si>
-    <t xml:space="preserve">Arshad Sons </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euro Model Town </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Season </t>
-  </si>
-  <si>
-    <t>Crown Market Singh pura</t>
-  </si>
-  <si>
-    <t>Jalal sons  Main Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raja Saab Wapda Town </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mb/SB Traders  Shadbagh </t>
-  </si>
-  <si>
-    <t>Sweera GT Road</t>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Naimat Khana</t>
+  </si>
+  <si>
+    <t>MS Traders (Risen)</t>
+  </si>
+  <si>
+    <t>Laraib LMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laraib Induction </t>
+  </si>
+  <si>
+    <t>Swera Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinix Warehouse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime Mart </t>
+  </si>
+  <si>
+    <t>LGS</t>
+  </si>
+  <si>
+    <t>Shahzad (asif Bro)</t>
+  </si>
+  <si>
+    <t>Rainbow</t>
   </si>
 </sst>
 </file>
@@ -250,7 +169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,6 +197,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -356,20 +281,19 @@
     <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,35 +614,40 @@
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="8.7265625" customWidth="1"/>
     <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.6328125" customWidth="1"/>
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="9.453125" customWidth="1"/>
-    <col min="17" max="17" width="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="9.453125" customWidth="1"/>
-    <col min="22" max="22" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.453125" customWidth="1"/>
-    <col min="24" max="24" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="9.453125" customWidth="1"/>
-    <col min="29" max="29" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2.90625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="2.90625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2.453125" customWidth="1"/>
+    <col min="15" max="15" width="6.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.453125" customWidth="1"/>
+    <col min="17" max="17" width="7.1796875" customWidth="1"/>
+    <col min="18" max="20" width="9.453125" customWidth="1"/>
+    <col min="21" max="21" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="8.26953125" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="3.08984375" hidden="1" customWidth="1"/>
+    <col min="25" max="28" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="8.6328125" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="5.26953125" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="2.90625" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.54296875" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="6.453125" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="2.90625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="8.6328125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="6.453125" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="8.6328125" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="7.54296875" hidden="1" customWidth="1"/>
     <col min="39" max="39" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8">
-        <v>46260</v>
+      <c r="A1" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>14</v>
@@ -773,16 +702,12 @@
         <v>0</v>
       </c>
       <c r="E2" s="14">
-        <v>46243</v>
-      </c>
-      <c r="F2" s="14">
-        <v>46253</v>
-      </c>
-      <c r="G2" s="14">
-        <v>46257</v>
-      </c>
+        <v>46270</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
       <c r="H2" s="14" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -889,106 +814,64 @@
         <v>70</v>
       </c>
       <c r="D3" s="1">
-        <v>6769</v>
+        <v>7895</v>
       </c>
       <c r="E3" s="1">
-        <v>8000</v>
-      </c>
-      <c r="F3" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="1">
         <f>SUM(D3:G3)</f>
-        <v>20769</v>
+        <v>13895</v>
       </c>
       <c r="I3" s="1">
-        <v>75</v>
-      </c>
-      <c r="J3" s="6"/>
+        <v>967</v>
+      </c>
+      <c r="J3" s="17"/>
       <c r="K3" s="1">
-        <v>144</v>
+        <v>438</v>
       </c>
       <c r="L3" s="1">
-        <v>92</v>
+        <v>355</v>
       </c>
       <c r="M3" s="1">
-        <v>260</v>
-      </c>
-      <c r="N3" s="1">
-        <v>770</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N3" s="6"/>
       <c r="O3" s="1">
-        <v>279</v>
-      </c>
-      <c r="P3" s="1">
-        <v>939</v>
-      </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="1">
-        <v>642</v>
-      </c>
-      <c r="S3" s="1">
-        <v>300</v>
-      </c>
-      <c r="T3" s="1">
-        <v>2268</v>
-      </c>
-      <c r="U3" s="1">
-        <v>184</v>
-      </c>
-      <c r="V3" s="6"/>
-      <c r="W3" s="1">
-        <v>250</v>
-      </c>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="1">
-        <v>250</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>390</v>
-      </c>
-      <c r="AA3" s="1">
-        <v>1041</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>422</v>
-      </c>
-      <c r="AC3" s="1">
-        <v>622</v>
-      </c>
-      <c r="AD3" s="1">
-        <v>270</v>
-      </c>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="1">
-        <v>337</v>
-      </c>
-      <c r="AG3" s="1">
-        <v>310</v>
-      </c>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="1">
-        <v>771</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>205</v>
-      </c>
-      <c r="AK3" s="1">
-        <v>1469</v>
-      </c>
-      <c r="AL3" s="1">
-        <v>622</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>12912</v>
+        <v>2418</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>7857</v>
+        <v>11477</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -999,106 +882,64 @@
         <v>70</v>
       </c>
       <c r="D4" s="1">
-        <v>3137</v>
+        <v>5619</v>
       </c>
       <c r="E4" s="1">
-        <v>8000</v>
-      </c>
-      <c r="F4" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G4" s="1">
-        <v>4000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="1">
         <f t="shared" ref="H4:H9" si="1">SUM(D4:G4)</f>
-        <v>19137</v>
+        <v>11619</v>
       </c>
       <c r="I4" s="1">
-        <v>40</v>
-      </c>
-      <c r="J4" s="6"/>
+        <v>888</v>
+      </c>
+      <c r="J4" s="17"/>
       <c r="K4" s="1">
-        <v>113</v>
+        <v>431</v>
       </c>
       <c r="L4" s="1">
-        <v>92</v>
+        <v>321</v>
       </c>
       <c r="M4" s="1">
-        <v>240</v>
-      </c>
-      <c r="N4" s="1">
-        <v>582</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N4" s="6"/>
       <c r="O4" s="1">
-        <v>481</v>
-      </c>
-      <c r="P4" s="1">
-        <v>1041</v>
-      </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="1">
-        <v>812</v>
-      </c>
-      <c r="S4" s="1">
-        <v>337</v>
-      </c>
-      <c r="T4" s="1">
-        <v>2028</v>
-      </c>
-      <c r="U4" s="1">
-        <v>158</v>
-      </c>
-      <c r="V4" s="6"/>
-      <c r="W4" s="1">
-        <v>363</v>
-      </c>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="1">
-        <v>258</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>421</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>1102</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>224</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>648</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>390</v>
-      </c>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="1">
-        <v>292</v>
-      </c>
-      <c r="AG4" s="1">
-        <v>196</v>
-      </c>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="1">
-        <v>1198</v>
-      </c>
-      <c r="AJ4" s="1">
-        <v>240</v>
-      </c>
-      <c r="AK4" s="1">
-        <v>1509</v>
-      </c>
-      <c r="AL4" s="1">
-        <v>673</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>13438</v>
+        <v>2324</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>5699</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -1109,106 +950,64 @@
         <v>70</v>
       </c>
       <c r="D5" s="1">
-        <v>7361</v>
+        <v>3200</v>
       </c>
       <c r="E5" s="1">
-        <v>8000</v>
-      </c>
-      <c r="F5" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="1">
         <f t="shared" si="1"/>
-        <v>21361</v>
+        <v>9200</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6"/>
+        <v>1073</v>
+      </c>
+      <c r="J5" s="17"/>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="M5" s="1">
         <v>240</v>
       </c>
-      <c r="N5" s="1">
-        <v>679</v>
-      </c>
+      <c r="N5" s="6"/>
       <c r="O5" s="1">
-        <v>179</v>
-      </c>
-      <c r="P5" s="1">
-        <v>3557</v>
-      </c>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="1">
-        <v>770</v>
-      </c>
-      <c r="S5" s="1">
-        <v>215</v>
-      </c>
-      <c r="T5" s="1">
-        <v>1290</v>
-      </c>
-      <c r="U5" s="1">
-        <v>339</v>
-      </c>
-      <c r="V5" s="6"/>
-      <c r="W5" s="1">
-        <v>305</v>
-      </c>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="1">
-        <v>116</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>742</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>1882</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>1066</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>519</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>159</v>
-      </c>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="1">
-        <v>447</v>
-      </c>
-      <c r="AG5" s="1">
-        <v>539</v>
-      </c>
-      <c r="AH5" s="6"/>
-      <c r="AI5" s="1">
-        <v>1384</v>
-      </c>
-      <c r="AJ5" s="1">
-        <v>627</v>
-      </c>
-      <c r="AK5" s="1">
-        <v>1859</v>
-      </c>
-      <c r="AL5" s="1">
-        <v>577</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>17491</v>
+        <v>2703</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>3870</v>
+        <v>6497</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1219,104 +1018,64 @@
         <v>120</v>
       </c>
       <c r="D6" s="1">
-        <v>13138</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1">
-        <v>12000</v>
-      </c>
-      <c r="G6" s="1">
-        <v>8000</v>
-      </c>
+        <v>5460</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="1">
         <f t="shared" si="1"/>
-        <v>33138</v>
+        <v>11460</v>
       </c>
       <c r="I6" s="1">
-        <v>228</v>
-      </c>
-      <c r="J6" s="6"/>
+        <v>921</v>
+      </c>
+      <c r="J6" s="17"/>
       <c r="K6" s="1">
-        <v>190</v>
+        <v>975</v>
       </c>
       <c r="L6" s="1">
-        <v>240</v>
+        <v>512</v>
       </c>
       <c r="M6" s="1">
-        <v>667</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1577</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N6" s="6"/>
       <c r="O6" s="1">
-        <v>539</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1264</v>
-      </c>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="1">
-        <v>947</v>
-      </c>
-      <c r="S6" s="1">
-        <v>574</v>
-      </c>
-      <c r="T6" s="1">
-        <v>5646</v>
-      </c>
-      <c r="U6" s="1">
-        <v>367</v>
-      </c>
-      <c r="V6" s="6"/>
-      <c r="W6" s="1">
-        <v>389</v>
-      </c>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="1">
-        <v>365</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>649</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>1304</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>1184</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>1052</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>520</v>
-      </c>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="1">
-        <v>621</v>
-      </c>
-      <c r="AG6" s="1">
-        <v>462</v>
-      </c>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="1">
-        <v>1383</v>
-      </c>
-      <c r="AJ6" s="1">
-        <v>504</v>
-      </c>
-      <c r="AK6" s="1">
-        <v>5341</v>
-      </c>
-      <c r="AL6" s="1">
-        <v>612</v>
-      </c>
+        <v>1104</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>26625</v>
+        <v>4005</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>6513</v>
+        <v>7455</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1327,106 +1086,64 @@
         <v>120</v>
       </c>
       <c r="D7" s="1">
-        <v>4387</v>
+        <v>7709</v>
       </c>
       <c r="E7" s="1">
-        <v>12000</v>
-      </c>
-      <c r="F7" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G7" s="1">
-        <v>12000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="1">
         <f t="shared" si="1"/>
-        <v>32387</v>
+        <v>13709</v>
       </c>
       <c r="I7" s="1">
-        <v>257</v>
-      </c>
-      <c r="J7" s="6"/>
+        <v>876</v>
+      </c>
+      <c r="J7" s="17"/>
       <c r="K7" s="1">
-        <v>175</v>
+        <v>892</v>
       </c>
       <c r="L7" s="1">
-        <v>170</v>
+        <v>440</v>
       </c>
       <c r="M7" s="1">
-        <v>730</v>
-      </c>
-      <c r="N7" s="1">
-        <v>1572</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N7" s="6"/>
       <c r="O7" s="1">
-        <v>398</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1562</v>
-      </c>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="1">
-        <v>1059</v>
-      </c>
-      <c r="S7" s="1">
-        <v>389</v>
-      </c>
-      <c r="T7" s="1">
-        <v>4384</v>
-      </c>
-      <c r="U7" s="1">
-        <v>255</v>
-      </c>
-      <c r="V7" s="6"/>
-      <c r="W7" s="1">
-        <v>602</v>
-      </c>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="1">
-        <v>330</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>794</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>1452</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>639</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>745</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>395</v>
-      </c>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="1">
-        <v>565</v>
-      </c>
-      <c r="AG7" s="1">
-        <v>322</v>
-      </c>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="1">
-        <v>1482</v>
-      </c>
-      <c r="AJ7" s="1">
-        <v>216</v>
-      </c>
-      <c r="AK7" s="1">
-        <v>5156</v>
-      </c>
-      <c r="AL7" s="1">
-        <v>556</v>
-      </c>
+        <v>1476</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>24205</v>
+        <v>4065</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>8182</v>
+        <v>9644</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1437,104 +1154,64 @@
         <v>120</v>
       </c>
       <c r="D8" s="1">
-        <v>15754</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1">
+        <v>3180</v>
+      </c>
+      <c r="E8" s="1">
         <v>12000</v>
       </c>
-      <c r="G8" s="1">
-        <v>12000</v>
-      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="1">
         <f t="shared" si="1"/>
-        <v>39754</v>
+        <v>15180</v>
       </c>
       <c r="I8" s="1">
-        <v>187</v>
-      </c>
-      <c r="J8" s="6"/>
+        <v>882</v>
+      </c>
+      <c r="J8" s="17"/>
       <c r="K8" s="1">
-        <v>235</v>
+        <v>655</v>
       </c>
       <c r="L8" s="1">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="M8" s="1">
-        <v>753</v>
-      </c>
-      <c r="N8" s="1">
-        <v>2315</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="N8" s="6"/>
       <c r="O8" s="1">
-        <v>946</v>
-      </c>
-      <c r="P8" s="1">
-        <v>2794</v>
-      </c>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="1">
-        <v>1402</v>
-      </c>
-      <c r="S8" s="1">
-        <v>602</v>
-      </c>
-      <c r="T8" s="1">
-        <v>6549</v>
-      </c>
-      <c r="U8" s="1">
-        <v>330</v>
-      </c>
-      <c r="V8" s="6"/>
-      <c r="W8" s="1">
-        <v>648</v>
-      </c>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="1">
-        <v>370</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>834</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>2908</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>1416</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>1246</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>702</v>
-      </c>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="1">
-        <v>735</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>840</v>
-      </c>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="1">
-        <v>2829</v>
-      </c>
-      <c r="AJ8" s="1">
-        <v>591</v>
-      </c>
-      <c r="AK8" s="1">
-        <v>5645</v>
-      </c>
-      <c r="AL8" s="1">
-        <v>726</v>
-      </c>
+        <v>2189</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>35823</v>
+        <v>4413</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>3931</v>
+        <v>10767</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1545,100 +1222,62 @@
         <v>60</v>
       </c>
       <c r="D9" s="1">
-        <v>34015</v>
+        <v>15644</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1">
         <f t="shared" si="1"/>
-        <v>34015</v>
+        <v>15644</v>
       </c>
       <c r="I9" s="1">
-        <v>252</v>
-      </c>
-      <c r="J9" s="6"/>
+        <v>320</v>
+      </c>
+      <c r="J9" s="17"/>
       <c r="K9" s="1">
-        <v>255</v>
+        <v>1283</v>
       </c>
       <c r="L9" s="1">
-        <v>292</v>
+        <v>506</v>
       </c>
       <c r="M9" s="1">
-        <v>447</v>
-      </c>
-      <c r="N9" s="1">
-        <v>2234</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N9" s="6"/>
       <c r="O9" s="1">
-        <v>263</v>
-      </c>
-      <c r="P9" s="1">
-        <v>148</v>
-      </c>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="1">
-        <v>652</v>
-      </c>
-      <c r="S9" s="1">
-        <v>472</v>
-      </c>
-      <c r="T9" s="1">
-        <v>4366</v>
-      </c>
-      <c r="U9" s="1">
-        <v>332</v>
-      </c>
-      <c r="V9" s="6"/>
-      <c r="W9" s="1">
-        <v>484</v>
-      </c>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="1">
-        <v>364</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>391</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>587</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>495</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>787</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>256</v>
-      </c>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="1">
-        <v>494</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>521</v>
-      </c>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="1">
-        <v>778</v>
-      </c>
-      <c r="AJ9" s="1">
-        <v>379</v>
-      </c>
-      <c r="AK9" s="1">
-        <v>2360</v>
-      </c>
-      <c r="AL9" s="1">
-        <v>1360</v>
-      </c>
+        <v>2168</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>18969</v>
+        <v>4713</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>15046</v>
+        <v>10931</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1648,27 +1287,27 @@
       <c r="C10" s="1"/>
       <c r="D10" s="5">
         <f>SUM(D3:D9)</f>
-        <v>84561</v>
+        <v>48707</v>
       </c>
       <c r="E10" s="5">
         <f>SUM(E3:E9)</f>
-        <v>36000</v>
+        <v>42000</v>
       </c>
       <c r="F10" s="5">
         <f>SUM(F3:F9)</f>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5">
         <f>SUM(G3:G9)</f>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5">
         <f>SUM(H3:H9)</f>
-        <v>200561</v>
+        <v>90707</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10:AN10" si="3">SUM(I3:I9)</f>
-        <v>1039</v>
+        <v>5927</v>
       </c>
       <c r="J10" s="5">
         <f t="shared" si="3"/>
@@ -1676,27 +1315,27 @@
       </c>
       <c r="K10" s="5">
         <f t="shared" si="3"/>
-        <v>1112</v>
+        <v>5169</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="3"/>
-        <v>1106</v>
+        <v>2628</v>
       </c>
       <c r="M10" s="5">
         <f t="shared" si="3"/>
-        <v>3337</v>
+        <v>2475</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" si="3"/>
-        <v>9729</v>
+        <v>0</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="3"/>
-        <v>3085</v>
+        <v>8442</v>
       </c>
       <c r="P10" s="5">
         <f t="shared" si="3"/>
-        <v>11305</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="3"/>
@@ -1704,19 +1343,19 @@
       </c>
       <c r="R10" s="5">
         <f t="shared" si="3"/>
-        <v>6284</v>
+        <v>0</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>2889</v>
+        <v>0</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="3"/>
-        <v>26531</v>
+        <v>0</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>1965</v>
+        <v>0</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="3"/>
@@ -1724,7 +1363,7 @@
       </c>
       <c r="W10" s="5">
         <f t="shared" si="3"/>
-        <v>3041</v>
+        <v>0</v>
       </c>
       <c r="X10" s="5">
         <f t="shared" si="3"/>
@@ -1732,27 +1371,27 @@
       </c>
       <c r="Y10" s="5">
         <f t="shared" si="3"/>
-        <v>2053</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="5">
         <f t="shared" si="3"/>
-        <v>4221</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="3"/>
-        <v>10276</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="3"/>
-        <v>5446</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="5">
         <f t="shared" si="3"/>
-        <v>5619</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="3"/>
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="3"/>
@@ -1760,11 +1399,11 @@
       </c>
       <c r="AF10" s="5">
         <f t="shared" si="3"/>
-        <v>3491</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="3"/>
-        <v>3190</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="3"/>
@@ -1772,27 +1411,27 @@
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="3"/>
-        <v>9825</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="5">
         <f t="shared" si="3"/>
-        <v>2762</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="3"/>
-        <v>23339</v>
+        <v>0</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="3"/>
-        <v>5126</v>
+        <v>0</v>
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>149463</v>
+        <v>24641</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>51098</v>
+        <v>66066</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1802,27 +1441,27 @@
       <c r="C11" s="1"/>
       <c r="D11" s="5">
         <f>D10/40</f>
-        <v>2114.0250000000001</v>
+        <v>1217.675</v>
       </c>
       <c r="E11" s="5">
         <f>E10/40</f>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="F11" s="5">
         <f>F10/40</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <f>G10/40</f>
-        <v>1000</v>
-      </c>
-      <c r="H11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15">
         <f>H10/40</f>
-        <v>5014.0249999999996</v>
+        <v>2267.6750000000002</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11:AN11" si="4">I10/40</f>
-        <v>25.975000000000001</v>
+        <v>148.17500000000001</v>
       </c>
       <c r="J11" s="5">
         <f t="shared" si="4"/>
@@ -1830,27 +1469,27 @@
       </c>
       <c r="K11" s="5">
         <f t="shared" si="4"/>
-        <v>27.8</v>
+        <v>129.22499999999999</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="4"/>
-        <v>27.65</v>
+        <v>65.7</v>
       </c>
       <c r="M11" s="5">
         <f t="shared" si="4"/>
-        <v>83.424999999999997</v>
+        <v>61.875</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="4"/>
-        <v>243.22499999999999</v>
+        <v>0</v>
       </c>
       <c r="O11" s="5">
         <f t="shared" si="4"/>
-        <v>77.125</v>
+        <v>211.05</v>
       </c>
       <c r="P11" s="5">
         <f t="shared" si="4"/>
-        <v>282.625</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="4"/>
@@ -1858,19 +1497,19 @@
       </c>
       <c r="R11" s="5">
         <f t="shared" si="4"/>
-        <v>157.1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="4"/>
-        <v>72.224999999999994</v>
+        <v>0</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
-        <v>663.27499999999998</v>
+        <v>0</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="4"/>
-        <v>49.125</v>
+        <v>0</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="4"/>
@@ -1878,7 +1517,7 @@
       </c>
       <c r="W11" s="5">
         <f t="shared" si="4"/>
-        <v>76.025000000000006</v>
+        <v>0</v>
       </c>
       <c r="X11" s="5">
         <f t="shared" si="4"/>
@@ -1886,27 +1525,27 @@
       </c>
       <c r="Y11" s="5">
         <f t="shared" si="4"/>
-        <v>51.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="5">
         <f t="shared" si="4"/>
-        <v>105.52500000000001</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="4"/>
-        <v>256.89999999999998</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="5">
         <f t="shared" si="4"/>
-        <v>136.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="5">
         <f t="shared" si="4"/>
-        <v>140.47499999999999</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="5">
         <f t="shared" si="4"/>
-        <v>67.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="5">
         <f t="shared" si="4"/>
@@ -1914,11 +1553,11 @@
       </c>
       <c r="AF11" s="5">
         <f t="shared" si="4"/>
-        <v>87.275000000000006</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="5">
         <f t="shared" si="4"/>
-        <v>79.75</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="5">
         <f t="shared" si="4"/>
@@ -1926,27 +1565,27 @@
       </c>
       <c r="AI11" s="5">
         <f t="shared" si="4"/>
-        <v>245.625</v>
+        <v>0</v>
       </c>
       <c r="AJ11" s="5">
         <f t="shared" si="4"/>
-        <v>69.05</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="4"/>
-        <v>583.47500000000002</v>
+        <v>0</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="4"/>
-        <v>128.15</v>
-      </c>
-      <c r="AM11" s="16">
-        <f t="shared" si="4"/>
-        <v>3736.5749999999998</v>
-      </c>
-      <c r="AN11" s="17">
-        <f t="shared" si="4"/>
-        <v>1277.45</v>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="15">
+        <f t="shared" si="4"/>
+        <v>616.02499999999998</v>
+      </c>
+      <c r="AN11" s="16">
+        <f t="shared" si="4"/>
+        <v>1651.65</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">
@@ -1981,615 +1620,383 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
-        <v>46239</v>
+        <v>46267</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1">
+        <v>120</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C14" s="1">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
-        <v>46239</v>
+        <v>46267</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
-        <v>46240</v>
+        <v>46268</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
-        <v>46240</v>
+        <v>46268</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
-        <v>46240</v>
+        <v>46268</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
-        <v>46240</v>
+        <v>46269</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
-        <v>46240</v>
+        <v>46269</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
-        <v>46240</v>
+        <v>46269</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C21" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
-        <v>46241</v>
+        <v>46269</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" s="1">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
-        <v>46241</v>
+        <v>46270</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1">
-        <v>16.5</v>
+        <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
-        <v>46242</v>
+        <v>46272</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1">
-        <v>21.3</v>
+        <v>9.625</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
-        <v>46242</v>
+        <v>46272</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" s="1">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
-        <v>46242</v>
+        <v>46272</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="1">
-        <v>21.975000000000001</v>
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="7">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="1">
+        <v>19</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="7">
+        <v>46272</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="1">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
+        <v>46272</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="7">
-        <v>46242</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="1">
-        <v>13</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28" s="7">
-        <v>46242</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="1">
-        <v>15</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29" s="7">
-        <v>46242</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="1">
-        <v>190</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="7">
-        <v>46244</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="1">
-        <v>15</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="7">
-        <v>46244</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="1">
-        <v>27</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="7">
-        <v>46244</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="1">
-        <v>10</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="7"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="7"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="7"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="7">
-        <v>46244</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="1">
-        <v>17</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A33" s="7"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="7">
-        <v>46244</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="1">
-        <v>9</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A34" s="7"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="7">
-        <v>46245</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="1">
-        <v>7</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A35" s="7"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="7">
-        <v>46245</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="1">
-        <v>14</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A36" s="7"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A37" s="7"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="1">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A38" s="7"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="1">
-        <v>6</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A39" s="7"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="1">
-        <v>16</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A40" s="7"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="1">
-        <v>17</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A41" s="7"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="1">
-        <v>450</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A42" s="7"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="7">
-        <v>46246</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="1">
-        <v>60</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A43" s="7"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="7">
-        <v>46247</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="1">
-        <v>10</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A44" s="7"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
-        <v>46247</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="1">
-        <v>7</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A45" s="7"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="7">
-        <v>46247</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="1">
-        <v>6</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A46" s="7"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="7">
-        <v>46249</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="1">
-        <v>5</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A47" s="7"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="7">
-        <v>46249</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="1">
-        <v>12.975</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A48" s="7"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="7">
-        <v>46249</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="1">
-        <v>23</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A49" s="7"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="7">
-        <v>46251</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="1">
-        <v>6</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A50" s="7"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="7">
-        <v>46252</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="1">
-        <v>4.9749999999999996</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A51" s="7"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="7">
-        <v>46252</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C52" s="1">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A52" s="7"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="7">
-        <v>46252</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C53" s="1">
-        <v>15</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A53" s="7"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="7">
-        <v>46252</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="1">
-        <v>12</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A54" s="7"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="7">
-        <v>46252</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="1">
-        <v>30</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A55" s="7"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -2718,7 +2125,7 @@
       <c r="B76" s="1"/>
       <c r="C76" s="4">
         <f>SUM(C14:C75)</f>
-        <v>1387.9749999999999</v>
+        <v>288.625</v>
       </c>
       <c r="D76" s="1"/>
     </row>

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A1866C-7492-407A-9243-C861163ED14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99AF332-1288-416C-878F-4EBCE8FA4DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -842,7 +842,9 @@
       <c r="O3" s="1">
         <v>438</v>
       </c>
-      <c r="P3" s="1"/>
+      <c r="P3" s="1">
+        <v>301</v>
+      </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -867,11 +869,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>2418</v>
+        <v>2719</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>11477</v>
+        <v>11176</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -910,7 +912,9 @@
       <c r="O4" s="1">
         <v>549</v>
       </c>
-      <c r="P4" s="1"/>
+      <c r="P4" s="1">
+        <v>246</v>
+      </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
@@ -935,11 +939,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>2324</v>
+        <v>2570</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>9295</v>
+        <v>9049</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -978,7 +982,9 @@
       <c r="O5" s="1">
         <v>518</v>
       </c>
-      <c r="P5" s="1"/>
+      <c r="P5" s="1">
+        <v>243</v>
+      </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -1003,11 +1009,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>2703</v>
+        <v>2946</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>6497</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1046,7 +1052,9 @@
       <c r="O6" s="1">
         <v>1104</v>
       </c>
-      <c r="P6" s="1"/>
+      <c r="P6" s="1">
+        <v>718</v>
+      </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -1071,11 +1079,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>4005</v>
+        <v>4723</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>7455</v>
+        <v>6737</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1114,7 +1122,9 @@
       <c r="O7" s="1">
         <v>1476</v>
       </c>
-      <c r="P7" s="1"/>
+      <c r="P7" s="1">
+        <v>457</v>
+      </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -1139,11 +1149,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>4065</v>
+        <v>4522</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>9644</v>
+        <v>9187</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1182,7 +1192,9 @@
       <c r="O8" s="1">
         <v>2189</v>
       </c>
-      <c r="P8" s="1"/>
+      <c r="P8" s="1">
+        <v>781</v>
+      </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -1207,11 +1219,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>4413</v>
+        <v>5194</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>10767</v>
+        <v>9986</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1248,7 +1260,9 @@
       <c r="O9" s="1">
         <v>2168</v>
       </c>
-      <c r="P9" s="1"/>
+      <c r="P9" s="1">
+        <v>651</v>
+      </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1273,11 +1287,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>4713</v>
+        <v>5364</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>10931</v>
+        <v>10280</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1335,7 +1349,7 @@
       </c>
       <c r="P10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3397</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="3"/>
@@ -1427,11 +1441,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>24641</v>
+        <v>28038</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>66066</v>
+        <v>62669</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1489,7 +1503,7 @@
       </c>
       <c r="P11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>84.924999999999997</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="4"/>
@@ -1581,11 +1595,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>616.02499999999998</v>
+        <v>700.95</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>1651.65</v>
+        <v>1566.7249999999999</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99AF332-1288-416C-878F-4EBCE8FA4DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7056A5F-04A9-4076-AD62-3762941614D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -845,7 +845,9 @@
       <c r="P3" s="1">
         <v>301</v>
       </c>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1">
+        <v>695</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -869,11 +871,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>2719</v>
+        <v>3414</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>11176</v>
+        <v>10481</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -915,7 +917,9 @@
       <c r="P4" s="1">
         <v>246</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1">
+        <v>835</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -939,11 +943,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>2570</v>
+        <v>3405</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>9049</v>
+        <v>8214</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -985,7 +989,9 @@
       <c r="P5" s="1">
         <v>243</v>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1">
+        <v>1478</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1009,11 +1015,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>2946</v>
+        <v>4424</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>6254</v>
+        <v>4776</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1055,7 +1061,9 @@
       <c r="P6" s="1">
         <v>718</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1">
+        <v>1828</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -1079,11 +1087,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>4723</v>
+        <v>6551</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>6737</v>
+        <v>4909</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1125,7 +1133,9 @@
       <c r="P7" s="1">
         <v>457</v>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1">
+        <v>2050</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -1149,11 +1159,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>4522</v>
+        <v>6572</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>9187</v>
+        <v>7137</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1195,7 +1205,9 @@
       <c r="P8" s="1">
         <v>781</v>
       </c>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="1">
+        <v>3306</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -1219,11 +1231,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>5194</v>
+        <v>8500</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>9986</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1263,7 +1275,9 @@
       <c r="P9" s="1">
         <v>651</v>
       </c>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1">
+        <v>324</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1287,11 +1301,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>5364</v>
+        <v>5688</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>10280</v>
+        <v>9956</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1353,7 +1367,7 @@
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10516</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="3"/>
@@ -1441,11 +1455,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>28038</v>
+        <v>38554</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>62669</v>
+        <v>52153</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1507,7 +1521,7 @@
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>262.89999999999998</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="4"/>
@@ -1595,11 +1609,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>700.95</v>
+        <v>963.85</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>1566.7249999999999</v>
+        <v>1303.825</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7056A5F-04A9-4076-AD62-3762941614D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DBDB8E-507F-4373-8C7C-EAA5F389CDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -90,46 +90,10 @@
     <t xml:space="preserve">Total </t>
   </si>
   <si>
-    <t>Delivered</t>
-  </si>
-  <si>
     <t>Primary</t>
   </si>
   <si>
-    <t xml:space="preserve">Jalal Sons </t>
-  </si>
-  <si>
     <t>Sep</t>
-  </si>
-  <si>
-    <t>Naimat Khana</t>
-  </si>
-  <si>
-    <t>MS Traders (Risen)</t>
-  </si>
-  <si>
-    <t>Laraib LMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laraib Induction </t>
-  </si>
-  <si>
-    <t>Swera Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinix Warehouse </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prime Mart </t>
-  </si>
-  <si>
-    <t>LGS</t>
-  </si>
-  <si>
-    <t>Shahzad (asif Bro)</t>
-  </si>
-  <si>
-    <t>Rainbow</t>
   </si>
 </sst>
 </file>
@@ -647,7 +611,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>14</v>
@@ -704,10 +668,12 @@
       <c r="E2" s="14">
         <v>46270</v>
       </c>
-      <c r="F2" s="14"/>
+      <c r="F2" s="14">
+        <v>46276</v>
+      </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -819,11 +785,13 @@
       <c r="E3" s="1">
         <v>6000</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1">
+        <v>6000</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1">
         <f>SUM(D3:G3)</f>
-        <v>13895</v>
+        <v>19895</v>
       </c>
       <c r="I3" s="1">
         <v>967</v>
@@ -848,7 +816,9 @@
       <c r="Q3" s="1">
         <v>695</v>
       </c>
-      <c r="R3" s="1"/>
+      <c r="R3" s="1">
+        <v>273</v>
+      </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -871,11 +841,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>3414</v>
+        <v>3687</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>10481</v>
+        <v>16208</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -891,11 +861,13 @@
       <c r="E4" s="1">
         <v>6000</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="1">
+        <v>4000</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1">
         <f t="shared" ref="H4:H9" si="1">SUM(D4:G4)</f>
-        <v>11619</v>
+        <v>15619</v>
       </c>
       <c r="I4" s="1">
         <v>888</v>
@@ -920,7 +892,9 @@
       <c r="Q4" s="1">
         <v>835</v>
       </c>
-      <c r="R4" s="1"/>
+      <c r="R4" s="1">
+        <v>267</v>
+      </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -943,11 +917,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>3405</v>
+        <v>3672</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>8214</v>
+        <v>11947</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -963,11 +937,13 @@
       <c r="E5" s="1">
         <v>6000</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="1">
+        <v>6000</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1">
         <f t="shared" si="1"/>
-        <v>9200</v>
+        <v>15200</v>
       </c>
       <c r="I5" s="1">
         <v>1073</v>
@@ -992,7 +968,9 @@
       <c r="Q5" s="1">
         <v>1478</v>
       </c>
-      <c r="R5" s="1"/>
+      <c r="R5" s="1">
+        <v>383</v>
+      </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
@@ -1015,11 +993,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>4424</v>
+        <v>4807</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>4776</v>
+        <v>10393</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1035,11 +1013,13 @@
       <c r="E6" s="1">
         <v>6000</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="1">
+        <v>6000</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
         <f t="shared" si="1"/>
-        <v>11460</v>
+        <v>17460</v>
       </c>
       <c r="I6" s="1">
         <v>921</v>
@@ -1064,7 +1044,9 @@
       <c r="Q6" s="1">
         <v>1828</v>
       </c>
-      <c r="R6" s="1"/>
+      <c r="R6" s="1">
+        <v>382</v>
+      </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
@@ -1087,11 +1069,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>6551</v>
+        <v>6933</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>4909</v>
+        <v>10527</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1107,11 +1089,13 @@
       <c r="E7" s="1">
         <v>6000</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1">
+        <v>4000</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1">
         <f t="shared" si="1"/>
-        <v>13709</v>
+        <v>17709</v>
       </c>
       <c r="I7" s="1">
         <v>876</v>
@@ -1136,7 +1120,9 @@
       <c r="Q7" s="1">
         <v>2050</v>
       </c>
-      <c r="R7" s="1"/>
+      <c r="R7" s="1">
+        <v>323</v>
+      </c>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1159,11 +1145,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>6572</v>
+        <v>6895</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>7137</v>
+        <v>10814</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1179,11 +1165,13 @@
       <c r="E8" s="1">
         <v>12000</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1">
+        <v>14000</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1">
         <f t="shared" si="1"/>
-        <v>15180</v>
+        <v>29180</v>
       </c>
       <c r="I8" s="1">
         <v>882</v>
@@ -1208,7 +1196,9 @@
       <c r="Q8" s="1">
         <v>3306</v>
       </c>
-      <c r="R8" s="1"/>
+      <c r="R8" s="1">
+        <v>595</v>
+      </c>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -1231,11 +1221,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>8500</v>
+        <v>9095</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>6680</v>
+        <v>20085</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1278,7 +1268,9 @@
       <c r="Q9" s="1">
         <v>324</v>
       </c>
-      <c r="R9" s="1"/>
+      <c r="R9" s="1">
+        <v>755</v>
+      </c>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -1301,11 +1293,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>5688</v>
+        <v>6443</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>9956</v>
+        <v>9201</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1323,7 +1315,7 @@
       </c>
       <c r="F10" s="5">
         <f>SUM(F3:F9)</f>
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="G10" s="5">
         <f>SUM(G3:G9)</f>
@@ -1331,7 +1323,7 @@
       </c>
       <c r="H10" s="5">
         <f>SUM(H3:H9)</f>
-        <v>90707</v>
+        <v>130707</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10:AN10" si="3">SUM(I3:I9)</f>
@@ -1371,7 +1363,7 @@
       </c>
       <c r="R10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2978</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
@@ -1455,11 +1447,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>38554</v>
+        <v>41532</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>52153</v>
+        <v>89175</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1477,7 +1469,7 @@
       </c>
       <c r="F11" s="5">
         <f>F10/40</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G11" s="5">
         <f>G10/40</f>
@@ -1485,7 +1477,7 @@
       </c>
       <c r="H11" s="15">
         <f>H10/40</f>
-        <v>2267.6750000000002</v>
+        <v>3267.6750000000002</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11:AN11" si="4">I10/40</f>
@@ -1525,7 +1517,7 @@
       </c>
       <c r="R11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>74.45</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="4"/>
@@ -1609,11 +1601,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>963.85</v>
+        <v>1038.3</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>1303.825</v>
+        <v>2229.375</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">
@@ -1647,228 +1639,100 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
-        <v>46267</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="1">
-        <v>120</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A14" s="7"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
-        <v>46267</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A15" s="7"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
-        <v>46268</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="1">
-        <v>34</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A16" s="7"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
-        <v>46268</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="1">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A17" s="7"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
-        <v>46268</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="1">
-        <v>11</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A18" s="7"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
-        <v>46269</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="1">
-        <v>17</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A19" s="7"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
-        <v>46269</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="7">
-        <v>46269</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="1">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A21" s="7"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
-        <v>46269</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A22" s="7"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
-        <v>46270</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="1">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A23" s="7"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="1">
-        <v>9.625</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A24" s="7"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="1">
-        <v>4</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A25" s="7"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="1">
-        <v>18</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A26" s="7"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="1">
-        <v>19</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A27" s="7"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="1">
-        <v>8</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A28" s="7"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="1">
-        <v>22</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A29" s="7"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="7"/>
@@ -2153,7 +2017,7 @@
       <c r="B76" s="1"/>
       <c r="C76" s="4">
         <f>SUM(C14:C75)</f>
-        <v>288.625</v>
+        <v>0</v>
       </c>
       <c r="D76" s="1"/>
     </row>

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DBDB8E-507F-4373-8C7C-EAA5F389CDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CF84DA-1ADC-49B5-A14E-60C8B84ABF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -819,7 +819,9 @@
       <c r="R3" s="1">
         <v>273</v>
       </c>
-      <c r="S3" s="1"/>
+      <c r="S3" s="1">
+        <v>314</v>
+      </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -841,11 +843,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>3687</v>
+        <v>4001</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>16208</v>
+        <v>15894</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -895,7 +897,9 @@
       <c r="R4" s="1">
         <v>267</v>
       </c>
-      <c r="S4" s="1"/>
+      <c r="S4" s="1">
+        <v>423</v>
+      </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -917,11 +921,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>3672</v>
+        <v>4095</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>11947</v>
+        <v>11524</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -971,7 +975,9 @@
       <c r="R5" s="1">
         <v>383</v>
       </c>
-      <c r="S5" s="1"/>
+      <c r="S5" s="1">
+        <v>784</v>
+      </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -993,11 +999,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>4807</v>
+        <v>5591</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>10393</v>
+        <v>9609</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1047,7 +1053,9 @@
       <c r="R6" s="1">
         <v>382</v>
       </c>
-      <c r="S6" s="1"/>
+      <c r="S6" s="1">
+        <v>703</v>
+      </c>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1069,11 +1077,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>6933</v>
+        <v>7636</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>10527</v>
+        <v>9824</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1123,7 +1131,9 @@
       <c r="R7" s="1">
         <v>323</v>
       </c>
-      <c r="S7" s="1"/>
+      <c r="S7" s="1">
+        <v>714</v>
+      </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -1145,11 +1155,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>6895</v>
+        <v>7609</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>10814</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1199,7 +1209,9 @@
       <c r="R8" s="1">
         <v>595</v>
       </c>
-      <c r="S8" s="1"/>
+      <c r="S8" s="1">
+        <v>1517</v>
+      </c>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
@@ -1221,11 +1233,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>9095</v>
+        <v>10612</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>20085</v>
+        <v>18568</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1271,7 +1283,9 @@
       <c r="R9" s="1">
         <v>755</v>
       </c>
-      <c r="S9" s="1"/>
+      <c r="S9" s="1">
+        <v>232</v>
+      </c>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -1293,11 +1307,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>6443</v>
+        <v>6675</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>9201</v>
+        <v>8969</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1367,7 +1381,7 @@
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4687</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="3"/>
@@ -1447,11 +1461,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>41532</v>
+        <v>46219</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>89175</v>
+        <v>84488</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1521,7 +1535,7 @@
       </c>
       <c r="S11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>117.175</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
@@ -1601,11 +1615,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>1038.3</v>
+        <v>1155.4749999999999</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>2229.375</v>
+        <v>2112.1999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CF84DA-1ADC-49B5-A14E-60C8B84ABF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D7392A-B66C-479C-B429-10EDB8C37547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -575,7 +575,7 @@
   <dimension ref="A1:AN76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6328125" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" customWidth="1"/>
@@ -591,10 +591,10 @@
     <col min="16" max="16" width="9.453125" customWidth="1"/>
     <col min="17" max="17" width="7.1796875" customWidth="1"/>
     <col min="18" max="20" width="9.453125" customWidth="1"/>
-    <col min="21" max="21" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="8.26953125" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="3.08984375" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="2.90625" customWidth="1"/>
+    <col min="22" max="22" width="8.26953125" customWidth="1"/>
+    <col min="23" max="23" width="9.453125" customWidth="1"/>
+    <col min="24" max="24" width="7.81640625" hidden="1" customWidth="1"/>
     <col min="25" max="28" width="9.453125" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="8.6328125" hidden="1" customWidth="1"/>
     <col min="30" max="30" width="5.26953125" hidden="1" customWidth="1"/>
@@ -822,9 +822,13 @@
       <c r="S3" s="1">
         <v>314</v>
       </c>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
+      <c r="T3" s="1">
+        <v>437</v>
+      </c>
+      <c r="U3" s="6"/>
+      <c r="V3" s="1">
+        <v>179</v>
+      </c>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -843,11 +847,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>4001</v>
+        <v>4617</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>15894</v>
+        <v>15278</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -900,9 +904,13 @@
       <c r="S4" s="1">
         <v>423</v>
       </c>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
+      <c r="T4" s="1">
+        <v>251</v>
+      </c>
+      <c r="U4" s="6"/>
+      <c r="V4" s="1">
+        <v>217</v>
+      </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -921,11 +929,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>4095</v>
+        <v>4563</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>11524</v>
+        <v>11056</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -978,9 +986,13 @@
       <c r="S5" s="1">
         <v>784</v>
       </c>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
+      <c r="T5" s="1">
+        <v>221</v>
+      </c>
+      <c r="U5" s="6"/>
+      <c r="V5" s="1">
+        <v>169</v>
+      </c>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -999,11 +1011,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>5591</v>
+        <v>5981</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>9609</v>
+        <v>9219</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1056,9 +1068,13 @@
       <c r="S6" s="1">
         <v>703</v>
       </c>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
+      <c r="T6" s="1">
+        <v>1166</v>
+      </c>
+      <c r="U6" s="6"/>
+      <c r="V6" s="1">
+        <v>340</v>
+      </c>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -1077,11 +1093,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>7636</v>
+        <v>9142</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>9824</v>
+        <v>8318</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1134,9 +1150,13 @@
       <c r="S7" s="1">
         <v>714</v>
       </c>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
+      <c r="T7" s="1">
+        <v>768</v>
+      </c>
+      <c r="U7" s="6"/>
+      <c r="V7" s="1">
+        <v>285</v>
+      </c>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -1155,11 +1175,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>7609</v>
+        <v>8662</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>10100</v>
+        <v>9047</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1212,9 +1232,13 @@
       <c r="S8" s="1">
         <v>1517</v>
       </c>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
+      <c r="T8" s="1">
+        <v>1134</v>
+      </c>
+      <c r="U8" s="6"/>
+      <c r="V8" s="1">
+        <v>291</v>
+      </c>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -1233,11 +1257,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>10612</v>
+        <v>12037</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>18568</v>
+        <v>17143</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1286,9 +1310,13 @@
       <c r="S9" s="1">
         <v>232</v>
       </c>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
+      <c r="T9" s="1">
+        <v>392</v>
+      </c>
+      <c r="U9" s="6"/>
+      <c r="V9" s="1">
+        <v>206</v>
+      </c>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
@@ -1307,11 +1335,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>6675</v>
+        <v>7273</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>8969</v>
+        <v>8371</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1385,7 +1413,7 @@
       </c>
       <c r="T10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4369</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
@@ -1393,7 +1421,7 @@
       </c>
       <c r="V10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1687</v>
       </c>
       <c r="W10" s="5">
         <f t="shared" si="3"/>
@@ -1461,11 +1489,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>46219</v>
+        <v>52275</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>84488</v>
+        <v>78432</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1539,7 +1567,7 @@
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>109.22499999999999</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="4"/>
@@ -1547,7 +1575,7 @@
       </c>
       <c r="V11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42.174999999999997</v>
       </c>
       <c r="W11" s="5">
         <f t="shared" si="4"/>
@@ -1615,11 +1643,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>1155.4749999999999</v>
+        <v>1306.875</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>2112.1999999999998</v>
+        <v>1960.8</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D7392A-B66C-479C-B429-10EDB8C37547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A49F16-42A3-4C6C-B260-B30B10947800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -829,7 +829,9 @@
       <c r="V3" s="1">
         <v>179</v>
       </c>
-      <c r="W3" s="1"/>
+      <c r="W3" s="1">
+        <v>864</v>
+      </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
@@ -847,11 +849,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>4617</v>
+        <v>5481</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>15278</v>
+        <v>14414</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -911,7 +913,9 @@
       <c r="V4" s="1">
         <v>217</v>
       </c>
-      <c r="W4" s="1"/>
+      <c r="W4" s="1">
+        <v>669</v>
+      </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -929,11 +933,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>4563</v>
+        <v>5232</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>11056</v>
+        <v>10387</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -993,7 +997,9 @@
       <c r="V5" s="1">
         <v>169</v>
       </c>
-      <c r="W5" s="1"/>
+      <c r="W5" s="1">
+        <v>734</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
@@ -1011,11 +1017,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>5981</v>
+        <v>6715</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>9219</v>
+        <v>8485</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1075,7 +1081,9 @@
       <c r="V6" s="1">
         <v>340</v>
       </c>
-      <c r="W6" s="1"/>
+      <c r="W6" s="1">
+        <v>676</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
@@ -1093,11 +1101,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>9142</v>
+        <v>9818</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>8318</v>
+        <v>7642</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1157,7 +1165,9 @@
       <c r="V7" s="1">
         <v>285</v>
       </c>
-      <c r="W7" s="1"/>
+      <c r="W7" s="1">
+        <v>765</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
@@ -1175,11 +1185,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>8662</v>
+        <v>9427</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>9047</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1239,7 +1249,9 @@
       <c r="V8" s="1">
         <v>291</v>
       </c>
-      <c r="W8" s="1"/>
+      <c r="W8" s="1">
+        <v>646</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
@@ -1257,11 +1269,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>12037</v>
+        <v>12683</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>17143</v>
+        <v>16497</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1317,7 +1329,9 @@
       <c r="V9" s="1">
         <v>206</v>
       </c>
-      <c r="W9" s="1"/>
+      <c r="W9" s="1">
+        <v>737</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
@@ -1335,11 +1349,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>7273</v>
+        <v>8010</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>8371</v>
+        <v>7634</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1425,7 +1439,7 @@
       </c>
       <c r="W10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5091</v>
       </c>
       <c r="X10" s="5">
         <f t="shared" si="3"/>
@@ -1489,11 +1503,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>52275</v>
+        <v>57366</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>78432</v>
+        <v>73341</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1579,7 +1593,7 @@
       </c>
       <c r="W11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>127.27500000000001</v>
       </c>
       <c r="X11" s="5">
         <f t="shared" si="4"/>
@@ -1643,11 +1657,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>1306.875</v>
+        <v>1434.15</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>1960.8</v>
+        <v>1833.5250000000001</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A49F16-42A3-4C6C-B260-B30B10947800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D7E3C1-8C65-4FF7-A199-942C750FCE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -594,8 +594,9 @@
     <col min="21" max="21" width="2.90625" customWidth="1"/>
     <col min="22" max="22" width="8.26953125" customWidth="1"/>
     <col min="23" max="23" width="9.453125" customWidth="1"/>
-    <col min="24" max="24" width="7.81640625" hidden="1" customWidth="1"/>
-    <col min="25" max="28" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="7.81640625" customWidth="1"/>
+    <col min="25" max="25" width="9.453125" customWidth="1"/>
+    <col min="26" max="28" width="9.453125" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="8.6328125" hidden="1" customWidth="1"/>
     <col min="30" max="30" width="5.26953125" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="2.90625" hidden="1" customWidth="1"/>
@@ -832,7 +833,9 @@
       <c r="W3" s="1">
         <v>864</v>
       </c>
-      <c r="X3" s="1"/>
+      <c r="X3" s="1">
+        <v>182</v>
+      </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
@@ -849,11 +852,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>5481</v>
+        <v>5663</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>14414</v>
+        <v>14232</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -916,7 +919,9 @@
       <c r="W4" s="1">
         <v>669</v>
       </c>
-      <c r="X4" s="1"/>
+      <c r="X4" s="1">
+        <v>126</v>
+      </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
@@ -933,11 +938,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>5232</v>
+        <v>5358</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>10387</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -1000,7 +1005,9 @@
       <c r="W5" s="1">
         <v>734</v>
       </c>
-      <c r="X5" s="1"/>
+      <c r="X5" s="1">
+        <v>80</v>
+      </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
@@ -1017,11 +1024,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>6715</v>
+        <v>6795</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>8485</v>
+        <v>8405</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1084,7 +1091,9 @@
       <c r="W6" s="1">
         <v>676</v>
       </c>
-      <c r="X6" s="1"/>
+      <c r="X6" s="1">
+        <v>292</v>
+      </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
@@ -1101,11 +1110,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>9818</v>
+        <v>10110</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>7642</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1168,7 +1177,9 @@
       <c r="W7" s="1">
         <v>765</v>
       </c>
-      <c r="X7" s="1"/>
+      <c r="X7" s="1">
+        <v>266</v>
+      </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
@@ -1185,11 +1196,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>9427</v>
+        <v>9693</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>8282</v>
+        <v>8016</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1252,7 +1263,9 @@
       <c r="W8" s="1">
         <v>646</v>
       </c>
-      <c r="X8" s="1"/>
+      <c r="X8" s="1">
+        <v>328</v>
+      </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
@@ -1269,11 +1282,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>12683</v>
+        <v>13011</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>16497</v>
+        <v>16169</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1332,7 +1345,9 @@
       <c r="W9" s="1">
         <v>737</v>
       </c>
-      <c r="X9" s="1"/>
+      <c r="X9" s="1">
+        <v>541</v>
+      </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
@@ -1349,11 +1364,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>8010</v>
+        <v>8551</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>7634</v>
+        <v>7093</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1443,7 +1458,7 @@
       </c>
       <c r="X10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1815</v>
       </c>
       <c r="Y10" s="5">
         <f t="shared" si="3"/>
@@ -1503,11 +1518,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>57366</v>
+        <v>59181</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>73341</v>
+        <v>71526</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1597,7 +1612,7 @@
       </c>
       <c r="X11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45.375</v>
       </c>
       <c r="Y11" s="5">
         <f t="shared" si="4"/>
@@ -1657,11 +1672,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>1434.15</v>
+        <v>1479.5250000000001</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>1833.5250000000001</v>
+        <v>1788.15</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D7E3C1-8C65-4FF7-A199-942C750FCE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9F76F-F9EA-4518-8525-1475F59BEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -836,7 +836,9 @@
       <c r="X3" s="1">
         <v>182</v>
       </c>
-      <c r="Y3" s="1"/>
+      <c r="Y3" s="1">
+        <v>1374</v>
+      </c>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
@@ -852,11 +854,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>5663</v>
+        <v>7037</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>14232</v>
+        <v>12858</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -922,7 +924,9 @@
       <c r="X4" s="1">
         <v>126</v>
       </c>
-      <c r="Y4" s="1"/>
+      <c r="Y4" s="1">
+        <v>1452</v>
+      </c>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
@@ -938,11 +942,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>5358</v>
+        <v>6810</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>10261</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -1008,7 +1012,9 @@
       <c r="X5" s="1">
         <v>80</v>
       </c>
-      <c r="Y5" s="1"/>
+      <c r="Y5" s="1">
+        <v>2616</v>
+      </c>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -1024,11 +1030,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>6795</v>
+        <v>9411</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>8405</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1094,7 +1100,9 @@
       <c r="X6" s="1">
         <v>292</v>
       </c>
-      <c r="Y6" s="1"/>
+      <c r="Y6" s="1">
+        <v>2702</v>
+      </c>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
@@ -1110,11 +1118,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>10110</v>
+        <v>12812</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>7350</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1180,7 +1188,9 @@
       <c r="X7" s="1">
         <v>266</v>
       </c>
-      <c r="Y7" s="1"/>
+      <c r="Y7" s="1">
+        <v>1487</v>
+      </c>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
@@ -1196,11 +1206,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>9693</v>
+        <v>11180</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>8016</v>
+        <v>6529</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1266,7 +1276,9 @@
       <c r="X8" s="1">
         <v>328</v>
       </c>
-      <c r="Y8" s="1"/>
+      <c r="Y8" s="1">
+        <v>2988</v>
+      </c>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
@@ -1282,11 +1294,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>13011</v>
+        <v>15999</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>16169</v>
+        <v>13181</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1348,7 +1360,9 @@
       <c r="X9" s="1">
         <v>541</v>
       </c>
-      <c r="Y9" s="1"/>
+      <c r="Y9" s="1">
+        <v>469</v>
+      </c>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
@@ -1364,11 +1378,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>8551</v>
+        <v>9020</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>7093</v>
+        <v>6624</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1462,7 +1476,7 @@
       </c>
       <c r="Y10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13088</v>
       </c>
       <c r="Z10" s="5">
         <f t="shared" si="3"/>
@@ -1518,11 +1532,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>59181</v>
+        <v>72269</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>71526</v>
+        <v>58438</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1616,7 +1630,7 @@
       </c>
       <c r="Y11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>327.2</v>
       </c>
       <c r="Z11" s="5">
         <f t="shared" si="4"/>
@@ -1672,11 +1686,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>1479.5250000000001</v>
+        <v>1806.7249999999999</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>1788.15</v>
+        <v>1460.95</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9F76F-F9EA-4518-8525-1475F59BEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B86FA1-2007-4F3C-ADB6-C12DFB0114A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -171,7 +171,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -203,11 +203,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -258,6 +269,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,14 +607,14 @@
     <col min="22" max="22" width="8.26953125" customWidth="1"/>
     <col min="23" max="23" width="9.453125" customWidth="1"/>
     <col min="24" max="24" width="7.81640625" customWidth="1"/>
-    <col min="25" max="25" width="9.453125" customWidth="1"/>
-    <col min="26" max="28" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="8.6328125" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.26953125" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="2.90625" hidden="1" customWidth="1"/>
+    <col min="25" max="27" width="9.453125" customWidth="1"/>
+    <col min="28" max="28" width="3.08984375" customWidth="1"/>
+    <col min="29" max="29" width="8.6328125" customWidth="1"/>
+    <col min="30" max="30" width="7" customWidth="1"/>
+    <col min="31" max="31" width="6.1796875" customWidth="1"/>
     <col min="32" max="32" width="7.54296875" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="6.453125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="2.90625" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="7.453125" hidden="1" customWidth="1"/>
     <col min="35" max="35" width="8.6328125" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="6.453125" hidden="1" customWidth="1"/>
     <col min="37" max="37" width="8.6328125" hidden="1" customWidth="1"/>
@@ -672,7 +684,9 @@
       <c r="F2" s="14">
         <v>46276</v>
       </c>
-      <c r="G2" s="14"/>
+      <c r="G2" s="14">
+        <v>46288</v>
+      </c>
       <c r="H2" s="14" t="s">
         <v>21</v>
       </c>
@@ -789,10 +803,12 @@
       <c r="F3" s="1">
         <v>6000</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1">
+        <v>4000</v>
+      </c>
       <c r="H3" s="1">
         <f>SUM(D3:G3)</f>
-        <v>19895</v>
+        <v>23895</v>
       </c>
       <c r="I3" s="1">
         <v>967</v>
@@ -839,11 +855,19 @@
       <c r="Y3" s="1">
         <v>1374</v>
       </c>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
+      <c r="Z3" s="1">
+        <v>275</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>215</v>
+      </c>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="1">
+        <v>72</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>1721</v>
+      </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
@@ -854,11 +878,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>7037</v>
+        <v>9320</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>12858</v>
+        <v>14575</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -877,10 +901,12 @@
       <c r="F4" s="1">
         <v>4000</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1">
+        <v>8000</v>
+      </c>
       <c r="H4" s="1">
         <f t="shared" ref="H4:H9" si="1">SUM(D4:G4)</f>
-        <v>15619</v>
+        <v>23619</v>
       </c>
       <c r="I4" s="1">
         <v>888</v>
@@ -927,11 +953,19 @@
       <c r="Y4" s="1">
         <v>1452</v>
       </c>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
+      <c r="Z4" s="1">
+        <v>328</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>370</v>
+      </c>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="1">
+        <v>75</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>1665</v>
+      </c>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
@@ -942,11 +976,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>6810</v>
+        <v>9248</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>8809</v>
+        <v>14371</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -965,10 +999,12 @@
       <c r="F5" s="1">
         <v>6000</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>10000</v>
+      </c>
       <c r="H5" s="1">
         <f t="shared" si="1"/>
-        <v>15200</v>
+        <v>25200</v>
       </c>
       <c r="I5" s="1">
         <v>1073</v>
@@ -1015,11 +1051,19 @@
       <c r="Y5" s="1">
         <v>2616</v>
       </c>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
+      <c r="Z5" s="1">
+        <v>425</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>699</v>
+      </c>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="1">
+        <v>133</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>2274</v>
+      </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
@@ -1030,11 +1074,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>9411</v>
+        <v>12942</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>5789</v>
+        <v>12258</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1053,10 +1097,12 @@
       <c r="F6" s="1">
         <v>6000</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>10000</v>
+      </c>
       <c r="H6" s="1">
         <f t="shared" si="1"/>
-        <v>17460</v>
+        <v>27460</v>
       </c>
       <c r="I6" s="1">
         <v>921</v>
@@ -1103,11 +1149,19 @@
       <c r="Y6" s="1">
         <v>2702</v>
       </c>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
+      <c r="Z6" s="1">
+        <v>726</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>623</v>
+      </c>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="1">
+        <v>254</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>2070</v>
+      </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
@@ -1118,11 +1172,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>12812</v>
+        <v>16485</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>4648</v>
+        <v>10975</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1141,10 +1195,12 @@
       <c r="F7" s="1">
         <v>4000</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>6000</v>
+      </c>
       <c r="H7" s="1">
         <f t="shared" si="1"/>
-        <v>17709</v>
+        <v>23709</v>
       </c>
       <c r="I7" s="1">
         <v>876</v>
@@ -1191,11 +1247,19 @@
       <c r="Y7" s="1">
         <v>1487</v>
       </c>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
+      <c r="Z7" s="1">
+        <v>549</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>612</v>
+      </c>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="1">
+        <v>198</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>1895</v>
+      </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
@@ -1206,11 +1270,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>11180</v>
+        <v>14434</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>6529</v>
+        <v>9275</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1229,10 +1293,12 @@
       <c r="F8" s="1">
         <v>14000</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>8000</v>
+      </c>
       <c r="H8" s="1">
         <f t="shared" si="1"/>
-        <v>29180</v>
+        <v>37180</v>
       </c>
       <c r="I8" s="1">
         <v>882</v>
@@ -1279,11 +1345,19 @@
       <c r="Y8" s="1">
         <v>2988</v>
       </c>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
+      <c r="Z8" s="1">
+        <v>515</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>1469</v>
+      </c>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="1">
+        <v>244</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>2934</v>
+      </c>
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
@@ -1294,11 +1368,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>15999</v>
+        <v>21161</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>13181</v>
+        <v>16019</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1363,9 +1437,11 @@
       <c r="Y9" s="1">
         <v>469</v>
       </c>
-      <c r="Z9" s="1"/>
+      <c r="Z9" s="1">
+        <v>40</v>
+      </c>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
+      <c r="AB9" s="6"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
@@ -1378,11 +1454,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>9020</v>
+        <v>9060</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>6624</v>
+        <v>6584</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1404,11 +1480,11 @@
       </c>
       <c r="G10" s="5">
         <f>SUM(G3:G9)</f>
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="H10" s="5">
         <f>SUM(H3:H9)</f>
-        <v>130707</v>
+        <v>176707</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10:AN10" si="3">SUM(I3:I9)</f>
@@ -1480,11 +1556,11 @@
       </c>
       <c r="Z10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2858</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3988</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="3"/>
@@ -1492,11 +1568,11 @@
       </c>
       <c r="AC10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>976</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12559</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="3"/>
@@ -1532,11 +1608,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>72269</v>
+        <v>92650</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>58438</v>
+        <v>84057</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1558,11 +1634,11 @@
       </c>
       <c r="G11" s="5">
         <f>G10/40</f>
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="H11" s="15">
         <f>H10/40</f>
-        <v>3267.6750000000002</v>
+        <v>4417.6750000000002</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11:AN11" si="4">I10/40</f>
@@ -1634,11 +1710,11 @@
       </c>
       <c r="Z11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>71.45</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>99.7</v>
       </c>
       <c r="AB11" s="5">
         <f t="shared" si="4"/>
@@ -1646,11 +1722,11 @@
       </c>
       <c r="AC11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="AD11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>313.97500000000002</v>
       </c>
       <c r="AE11" s="5">
         <f t="shared" si="4"/>
@@ -1686,11 +1762,11 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>1806.7249999999999</v>
+        <v>2316.25</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>1460.95</v>
+        <v>2101.4250000000002</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">
@@ -1704,6 +1780,7 @@
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
+      <c r="M12" s="20"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B86FA1-2007-4F3C-ADB6-C12DFB0114A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED80155-2192-4F1A-891E-30F3663DAC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -263,13 +263,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,13 +612,13 @@
     <col min="29" max="29" width="8.6328125" customWidth="1"/>
     <col min="30" max="30" width="7" customWidth="1"/>
     <col min="31" max="31" width="6.1796875" customWidth="1"/>
-    <col min="32" max="32" width="7.54296875" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="6.453125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="7.453125" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="8.6328125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="6.453125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="8.6328125" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="7.54296875" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.54296875" customWidth="1"/>
+    <col min="33" max="33" width="6.453125" customWidth="1"/>
+    <col min="34" max="34" width="7.453125" customWidth="1"/>
+    <col min="35" max="35" width="8.6328125" customWidth="1"/>
+    <col min="36" max="36" width="6.453125" customWidth="1"/>
+    <col min="37" max="37" width="8.6328125" customWidth="1"/>
+    <col min="38" max="38" width="7.54296875" customWidth="1"/>
     <col min="39" max="39" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -626,47 +626,47 @@
       <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="19"/>
     </row>
     <row r="2" spans="1:40" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
@@ -1770,17 +1770,17 @@
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
-      <c r="M12" s="20"/>
+      <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED80155-2192-4F1A-891E-30F3663DAC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC315F13-81F3-4CDC-B7E2-DE0A60908C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -868,21 +868,37 @@
       <c r="AD3" s="1">
         <v>1721</v>
       </c>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-      <c r="AH3" s="1"/>
-      <c r="AI3" s="1"/>
-      <c r="AJ3" s="1"/>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="1"/>
+      <c r="AE3" s="1">
+        <v>342</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>221</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>773</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>122</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>743</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>468</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>468</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>566</v>
+      </c>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>9320</v>
+        <v>13023</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>14575</v>
+        <v>10872</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -966,21 +982,37 @@
       <c r="AD4" s="1">
         <v>1665</v>
       </c>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
+      <c r="AE4" s="1">
+        <v>457</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>238</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>685</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>150</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>637</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>540</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>540</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>503</v>
+      </c>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>9248</v>
+        <v>12998</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>14371</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -1064,21 +1096,37 @@
       <c r="AD5" s="1">
         <v>2274</v>
       </c>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="1"/>
-      <c r="AI5" s="1"/>
-      <c r="AJ5" s="1"/>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="1"/>
+      <c r="AE5" s="1">
+        <v>501</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>701</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>834</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>234</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>1042</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>890</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>890</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>710</v>
+      </c>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>12942</v>
+        <v>18744</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>12258</v>
+        <v>6456</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1115,7 +1163,7 @@
         <v>512</v>
       </c>
       <c r="M6" s="1">
-        <v>493</v>
+        <v>1213</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="1">
@@ -1162,21 +1210,37 @@
       <c r="AD6" s="1">
         <v>2070</v>
       </c>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="1"/>
-      <c r="AI6" s="1"/>
-      <c r="AJ6" s="1"/>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="1"/>
+      <c r="AE6" s="1">
+        <v>684</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>399</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>1151</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>288</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>1677</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>1446</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>1446</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>627</v>
+      </c>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>16485</v>
+        <v>24923</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>10975</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1213,7 +1277,7 @@
         <v>440</v>
       </c>
       <c r="M7" s="1">
-        <v>381</v>
+        <v>1181</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="1">
@@ -1260,21 +1324,37 @@
       <c r="AD7" s="1">
         <v>1895</v>
       </c>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="1"/>
-      <c r="AI7" s="1"/>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="1"/>
-      <c r="AL7" s="1"/>
+      <c r="AE7" s="1">
+        <v>593</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>1209</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>1133</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>267</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>1494</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>1265</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>1265</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>524</v>
+      </c>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>14434</v>
+        <v>22984</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>9275</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1311,7 +1391,7 @@
         <v>117</v>
       </c>
       <c r="M8" s="1">
-        <v>570</v>
+        <v>1450</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="1">
@@ -1358,21 +1438,37 @@
       <c r="AD8" s="1">
         <v>2934</v>
       </c>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="1"/>
-      <c r="AI8" s="1"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="1"/>
-      <c r="AL8" s="1"/>
+      <c r="AE8" s="1">
+        <v>696</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>1068</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>1356</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>451</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>1965</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>1535</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>1535</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>808</v>
+      </c>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>21161</v>
+        <v>31455</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>16019</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1445,7 +1541,9 @@
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
+      <c r="AF9" s="1">
+        <v>17</v>
+      </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
@@ -1454,11 +1552,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>9060</v>
+        <v>9077</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>6584</v>
+        <v>6567</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1504,7 +1602,7 @@
       </c>
       <c r="M10" s="5">
         <f t="shared" si="3"/>
-        <v>2475</v>
+        <v>4875</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" si="3"/>
@@ -1576,43 +1674,43 @@
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3273</v>
       </c>
       <c r="AF10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3853</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5932</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7558</v>
       </c>
       <c r="AJ10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6144</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6144</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3738</v>
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>92650</v>
+        <v>133204</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>84057</v>
+        <v>43503</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1658,7 +1756,7 @@
       </c>
       <c r="M11" s="5">
         <f t="shared" si="4"/>
-        <v>61.875</v>
+        <v>121.875</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="4"/>
@@ -1730,43 +1828,43 @@
       </c>
       <c r="AE11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>81.825000000000003</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96.325000000000003</v>
       </c>
       <c r="AG11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>148.30000000000001</v>
       </c>
       <c r="AH11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="AI11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>188.95</v>
       </c>
       <c r="AJ11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>153.6</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>153.6</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>93.45</v>
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>2316.25</v>
+        <v>3330.1</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>2101.4250000000002</v>
+        <v>1087.575</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC315F13-81F3-4CDC-B7E2-DE0A60908C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1297F39-856B-417B-8418-2DC260924F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -1766,7 +1766,7 @@
         <f t="shared" si="4"/>
         <v>211.05</v>
       </c>
-      <c r="P11" s="5">
+      <c r="P11" s="15">
         <f t="shared" si="4"/>
         <v>84.924999999999997</v>
       </c>
@@ -1774,15 +1774,15 @@
         <f t="shared" si="4"/>
         <v>262.89999999999998</v>
       </c>
-      <c r="R11" s="5">
+      <c r="R11" s="15">
         <f t="shared" si="4"/>
         <v>74.45</v>
       </c>
-      <c r="S11" s="5">
+      <c r="S11" s="15">
         <f t="shared" si="4"/>
         <v>117.175</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11" s="15">
         <f t="shared" si="4"/>
         <v>109.22499999999999</v>
       </c>
@@ -1794,15 +1794,15 @@
         <f t="shared" si="4"/>
         <v>42.174999999999997</v>
       </c>
-      <c r="W11" s="5">
+      <c r="W11" s="15">
         <f t="shared" si="4"/>
         <v>127.27500000000001</v>
       </c>
-      <c r="X11" s="5">
+      <c r="X11" s="15">
         <f t="shared" si="4"/>
         <v>45.375</v>
       </c>
-      <c r="Y11" s="5">
+      <c r="Y11" s="15">
         <f t="shared" si="4"/>
         <v>327.2</v>
       </c>
@@ -1810,7 +1810,7 @@
         <f t="shared" si="4"/>
         <v>71.45</v>
       </c>
-      <c r="AA11" s="5">
+      <c r="AA11" s="15">
         <f t="shared" si="4"/>
         <v>99.7</v>
       </c>
@@ -1822,7 +1822,7 @@
         <f t="shared" si="4"/>
         <v>24.4</v>
       </c>
-      <c r="AD11" s="5">
+      <c r="AD11" s="15">
         <f t="shared" si="4"/>
         <v>313.97500000000002</v>
       </c>
@@ -1838,11 +1838,11 @@
         <f t="shared" si="4"/>
         <v>148.30000000000001</v>
       </c>
-      <c r="AH11" s="5">
+      <c r="AH11" s="15">
         <f t="shared" si="4"/>
         <v>37.799999999999997</v>
       </c>
-      <c r="AI11" s="5">
+      <c r="AI11" s="15">
         <f t="shared" si="4"/>
         <v>188.95</v>
       </c>
@@ -1850,7 +1850,7 @@
         <f t="shared" si="4"/>
         <v>153.6</v>
       </c>
-      <c r="AK11" s="5">
+      <c r="AK11" s="15">
         <f t="shared" si="4"/>
         <v>153.6</v>
       </c>
@@ -1909,104 +1909,128 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
+      <c r="H15">
+        <f>H3/40</f>
+        <v>597.375</v>
+      </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H16">
+        <f t="shared" ref="H16:H21" si="5">H4/40</f>
+        <v>590.47500000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H17">
+        <f t="shared" si="5"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H18">
+        <f t="shared" si="5"/>
+        <v>686.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="7"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H19">
+        <f t="shared" si="5"/>
+        <v>592.72500000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H20">
+        <f t="shared" si="5"/>
+        <v>929.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="7"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="7"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="7"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="7"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="7"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="7"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="7"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="7"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>

--- a/Sep_2026/daily Reports/Monthly.xlsx
+++ b/Sep_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1297F39-856B-417B-8418-2DC260924F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1353DA-5B77-409B-BBBD-EC31B921AFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -1909,9 +1909,8 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="H15">
-        <f>H3/40</f>
-        <v>597.375</v>
+      <c r="I15">
+        <v>16000</v>
       </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.35">
@@ -1919,118 +1918,113 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="H16">
-        <f t="shared" ref="H16:H21" si="5">H4/40</f>
-        <v>590.47500000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="H17">
-        <f t="shared" si="5"/>
-        <v>630</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="H18">
-        <f t="shared" si="5"/>
-        <v>686.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="7"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="H19">
-        <f t="shared" si="5"/>
-        <v>592.72500000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="H20">
-        <f t="shared" si="5"/>
-        <v>929.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="7"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="7"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="7"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="7"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="7"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="7"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="7"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="7"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
